--- a/ReferencesSelection.xlsx
+++ b/ReferencesSelection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\33993\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A574B4-9EB1-49C5-8ABB-1A65C9204838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E2AFBF-9A29-41DC-A1E8-FDDABBBC442D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{8109751A-43CE-4E38-9133-E6D6471D16C1}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2740" uniqueCount="1037">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2791" uniqueCount="1042">
   <si>
     <t>No.</t>
   </si>
@@ -3322,6 +3322,26 @@
   </si>
   <si>
     <t>Understanding teachers’ perspectives on ChatGPT-generated assignments in higher education</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chen</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cruz-Jesus</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lodge</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pham</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Singh</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3762,7 +3782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92D08E4-295D-434E-BB35-1D7E5C9F056F}">
-  <dimension ref="A1:E349"/>
+  <dimension ref="A1:E367"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.08203125" bestFit="1" customWidth="1"/>
@@ -9594,6 +9614,283 @@
       </c>
       <c r="E349" t="s">
         <v>231</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" ht="17.5" x14ac:dyDescent="0.3">
+      <c r="A351" s="1" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A352" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B352" t="s">
+        <v>1</v>
+      </c>
+      <c r="C352" t="s">
+        <v>2</v>
+      </c>
+      <c r="D352" t="s">
+        <v>3</v>
+      </c>
+      <c r="E352" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A353">
+        <v>1</v>
+      </c>
+      <c r="B353" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C353">
+        <v>2020</v>
+      </c>
+      <c r="D353" t="s">
+        <v>11</v>
+      </c>
+      <c r="E353" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A354">
+        <v>2</v>
+      </c>
+      <c r="B354" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C354">
+        <v>2020</v>
+      </c>
+      <c r="D354" t="s">
+        <v>14</v>
+      </c>
+      <c r="E354" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A355">
+        <v>3</v>
+      </c>
+      <c r="B355" t="s">
+        <v>16</v>
+      </c>
+      <c r="C355">
+        <v>2020</v>
+      </c>
+      <c r="D355" t="s">
+        <v>17</v>
+      </c>
+      <c r="E355" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A356">
+        <v>4</v>
+      </c>
+      <c r="B356" t="s">
+        <v>28</v>
+      </c>
+      <c r="C356">
+        <v>2020</v>
+      </c>
+      <c r="D356" t="s">
+        <v>29</v>
+      </c>
+      <c r="E356" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A357">
+        <v>5</v>
+      </c>
+      <c r="B357" t="s">
+        <v>973</v>
+      </c>
+      <c r="C357">
+        <v>2020</v>
+      </c>
+      <c r="D357" t="s">
+        <v>32</v>
+      </c>
+      <c r="E357" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A358">
+        <v>6</v>
+      </c>
+      <c r="B358" t="s">
+        <v>37</v>
+      </c>
+      <c r="C358">
+        <v>2021</v>
+      </c>
+      <c r="D358" t="s">
+        <v>38</v>
+      </c>
+      <c r="E358" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A359">
+        <v>7</v>
+      </c>
+      <c r="B359" t="s">
+        <v>500</v>
+      </c>
+      <c r="C359">
+        <v>2021</v>
+      </c>
+      <c r="D359" t="s">
+        <v>53</v>
+      </c>
+      <c r="E359" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A360">
+        <v>8</v>
+      </c>
+      <c r="B360" t="s">
+        <v>578</v>
+      </c>
+      <c r="C360">
+        <v>2021</v>
+      </c>
+      <c r="D360" t="s">
+        <v>62</v>
+      </c>
+      <c r="E360" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A361">
+        <v>9</v>
+      </c>
+      <c r="B361" t="s">
+        <v>76</v>
+      </c>
+      <c r="C361">
+        <v>2022</v>
+      </c>
+      <c r="D361" t="s">
+        <v>77</v>
+      </c>
+      <c r="E361" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A362">
+        <v>10</v>
+      </c>
+      <c r="B362" t="s">
+        <v>974</v>
+      </c>
+      <c r="C362">
+        <v>2022</v>
+      </c>
+      <c r="D362" t="s">
+        <v>663</v>
+      </c>
+      <c r="E362" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A363">
+        <v>11</v>
+      </c>
+      <c r="B363" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C363">
+        <v>2023</v>
+      </c>
+      <c r="D363" t="s">
+        <v>666</v>
+      </c>
+      <c r="E363" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A364">
+        <v>12</v>
+      </c>
+      <c r="B364" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C364">
+        <v>2023</v>
+      </c>
+      <c r="D364" t="s">
+        <v>669</v>
+      </c>
+      <c r="E364" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A365">
+        <v>13</v>
+      </c>
+      <c r="B365" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C365">
+        <v>2023</v>
+      </c>
+      <c r="D365" t="s">
+        <v>672</v>
+      </c>
+      <c r="E365" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A366">
+        <v>14</v>
+      </c>
+      <c r="B366" t="s">
+        <v>674</v>
+      </c>
+      <c r="C366">
+        <v>2023</v>
+      </c>
+      <c r="D366" t="s">
+        <v>675</v>
+      </c>
+      <c r="E366" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A367">
+        <v>15</v>
+      </c>
+      <c r="B367" t="s">
+        <v>677</v>
+      </c>
+      <c r="C367">
+        <v>2023</v>
+      </c>
+      <c r="D367" t="s">
+        <v>678</v>
+      </c>
+      <c r="E367" t="s">
+        <v>679</v>
       </c>
     </row>
   </sheetData>
